--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.94739</v>
+        <v>16.83959</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98335</v>
+        <v>16.61611</v>
       </c>
       <c r="E2" t="n">
-        <v>16.82007</v>
+        <v>16.80427</v>
       </c>
       <c r="F2" t="n">
-        <v>41.60284</v>
+        <v>42.9439</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05076</v>
+        <v>0.05122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84565</v>
+        <v>1.81036</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.68345</v>
+        <v>17.16809</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69475</v>
+        <v>16.39689</v>
       </c>
       <c r="E3" t="n">
-        <v>16.98507</v>
+        <v>16.73886</v>
       </c>
       <c r="F3" t="n">
-        <v>43.38665</v>
+        <v>43.02403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05117</v>
+        <v>0.05116</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86204</v>
+        <v>1.84592</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.00178</v>
+        <v>17.0998</v>
       </c>
       <c r="D4" t="n">
-        <v>16.58284</v>
+        <v>17.01492</v>
       </c>
       <c r="E4" t="n">
-        <v>16.57554</v>
+        <v>17.06588</v>
       </c>
       <c r="F4" t="n">
-        <v>43.67551</v>
+        <v>42.54238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05042</v>
+        <v>0.05007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82135</v>
+        <v>1.81536</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.94127</v>
+        <v>16.74183</v>
       </c>
       <c r="D6" t="n">
-        <v>15.96422</v>
+        <v>16.2112</v>
       </c>
       <c r="E6" t="n">
-        <v>16.25991</v>
+        <v>16.28959</v>
       </c>
       <c r="F6" t="n">
-        <v>21.94703</v>
+        <v>22.31418</v>
       </c>
       <c r="G6" t="n">
-        <v>35.16087</v>
+        <v>34.6917</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90708</v>
+        <v>16.54987</v>
       </c>
       <c r="D7" t="n">
-        <v>15.7629</v>
+        <v>15.94571</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65335</v>
+        <v>16.5225</v>
       </c>
       <c r="F7" t="n">
-        <v>21.79297</v>
+        <v>21.87007</v>
       </c>
       <c r="G7" t="n">
-        <v>34.99167</v>
+        <v>34.27773</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.11269</v>
+        <v>16.79371</v>
       </c>
       <c r="D8" t="n">
-        <v>15.87047</v>
+        <v>16.19794</v>
       </c>
       <c r="E8" t="n">
-        <v>16.15844</v>
+        <v>16.4886</v>
       </c>
       <c r="F8" t="n">
-        <v>21.64393</v>
+        <v>21.57601</v>
       </c>
       <c r="G8" t="n">
-        <v>34.0236</v>
+        <v>34.30447</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.602</v>
+        <v>0.59609</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12705</v>
+        <v>1.10898</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.61128</v>
+        <v>0.60981</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11474</v>
+        <v>1.11238</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60402</v>
+        <v>0.61777</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1328</v>
+        <v>1.13241</v>
       </c>
     </row>
   </sheetData>
